--- a/experiment1.xlsx
+++ b/experiment1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\CTOP\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D931AEA0-70DA-40DF-A453-36A03B731635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E264F5F0-07E1-4B7A-9B14-92424F48D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-4270" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-6810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="set2" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
   <si>
     <t>LDMA1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t>Index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDMA_OX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDMA_ERX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -370,15 +382,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,34 +673,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="I1" s="3"/>
+      <c r="K1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -695,27 +718,49 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -726,22 +771,49 @@
         <v>5.4767284229552562</v>
       </c>
       <c r="D3">
+        <v>-14.36108489627253</v>
+      </c>
+      <c r="E3">
         <v>9.0090090090090086E-2</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.32535020334386888</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
+        <v>-15.205341006138415</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>0.18978761861725341</v>
       </c>
-      <c r="H3">
+      <c r="J3">
+        <v>-6.0300721096805789</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0.74107546317216855</v>
+      </c>
+      <c r="M3">
+        <v>-12.546741636935757</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>2.2864889290555768</v>
+      </c>
+      <c r="P3">
+        <v>2.803234910587348</v>
+      </c>
+      <c r="Q3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -752,22 +824,49 @@
         <v>3.125</v>
       </c>
       <c r="D4">
+        <v>3.7085604281681497</v>
+      </c>
+      <c r="E4">
         <v>0.52770448548812665</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.61619718309859151</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
+        <v>-5.6207834243918837</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>0.14964788732394768</v>
       </c>
-      <c r="H4">
+      <c r="J4">
+        <v>-14.541664603140452</v>
+      </c>
+      <c r="K4">
+        <v>0.61565523306948111</v>
+      </c>
+      <c r="L4">
+        <v>0.86267605633802424</v>
+      </c>
+      <c r="M4">
+        <v>-10.680229673030722</v>
+      </c>
+      <c r="N4">
+        <v>1.4072119613016711</v>
+      </c>
+      <c r="O4">
+        <v>1.6725352112676055</v>
+      </c>
+      <c r="P4">
+        <v>0.60125128508907388</v>
+      </c>
+      <c r="Q4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -778,22 +877,49 @@
         <v>2.3304203079483976</v>
       </c>
       <c r="D5">
+        <v>-3.9808075208724816</v>
+      </c>
+      <c r="E5">
         <v>0.49916805324459235</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.59092800665833611</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
+        <v>-1.6613552728317771</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6.6583437369950441E-2</v>
       </c>
-      <c r="H5">
+      <c r="J5">
+        <v>-6.8253188911420484</v>
+      </c>
+      <c r="K5">
+        <v>0.83194675540765384</v>
+      </c>
+      <c r="L5">
+        <v>1.0486891385767714</v>
+      </c>
+      <c r="M5">
+        <v>-8.731443849246002</v>
+      </c>
+      <c r="N5">
+        <v>1.1647254575707155</v>
+      </c>
+      <c r="O5">
+        <v>1.5314190595089547</v>
+      </c>
+      <c r="P5">
+        <v>-5.1205170035078451</v>
+      </c>
+      <c r="Q5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -804,22 +930,49 @@
         <v>2.1369678613494756</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>8.1391061431160825</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>0.1430254080430606</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>7.0026324062494067</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>5.0479555779901493E-2</v>
       </c>
-      <c r="H6">
+      <c r="J6">
+        <v>-6.4641114630758585</v>
+      </c>
+      <c r="K6">
+        <v>1.0915197313182201</v>
+      </c>
+      <c r="L6">
+        <v>1.3377082281675807</v>
+      </c>
+      <c r="M6">
+        <v>-12.366158600607676</v>
+      </c>
+      <c r="N6">
+        <v>1.3434089000839631</v>
+      </c>
+      <c r="O6">
+        <v>1.6237590442537402</v>
+      </c>
+      <c r="P6">
+        <v>-6.0636358246521844</v>
+      </c>
+      <c r="Q6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -830,22 +983,49 @@
         <v>4.8872502786590077</v>
       </c>
       <c r="D7">
+        <v>1.6721099015709278</v>
+      </c>
+      <c r="E7">
         <v>0.17079419299743809</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.12003772614249024</v>
       </c>
-      <c r="F7">
+      <c r="G7">
+        <v>-6.1969294775640513</v>
+      </c>
+      <c r="H7">
         <v>0.17079419299743809</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>0.1714824659178599</v>
       </c>
-      <c r="H7">
+      <c r="J7">
+        <v>-10.515429182865537</v>
+      </c>
+      <c r="K7">
+        <v>0.76857386848847142</v>
+      </c>
+      <c r="L7">
+        <v>1.2089513847209046</v>
+      </c>
+      <c r="M7">
+        <v>-2.6727749126896363</v>
+      </c>
+      <c r="N7">
+        <v>0.85397096498719038</v>
+      </c>
+      <c r="O7">
+        <v>2.6236817285432488</v>
+      </c>
+      <c r="P7">
+        <v>6.3131934667449343</v>
+      </c>
+      <c r="Q7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -856,22 +1036,49 @@
         <v>2.084347120843475</v>
       </c>
       <c r="D8">
+        <v>3.9717828462050533</v>
+      </c>
+      <c r="E8">
         <v>8.1037277147487846E-2</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.15409570154096439</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
+        <v>-3.1183272644201216</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>3.2441200324419384E-2</v>
       </c>
-      <c r="H8">
+      <c r="J8">
+        <v>-5.9833904157877713</v>
+      </c>
+      <c r="K8">
+        <v>0.72933549432739064</v>
+      </c>
+      <c r="L8">
+        <v>0.98134630981345572</v>
+      </c>
+      <c r="M8">
+        <v>-2.5023261482214654</v>
+      </c>
+      <c r="N8">
+        <v>1.0534846029173419</v>
+      </c>
+      <c r="O8">
+        <v>1.47607461476075</v>
+      </c>
+      <c r="P8">
+        <v>-0.87152950296213139</v>
+      </c>
+      <c r="Q8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -882,22 +1089,49 @@
         <v>2.1534437663469959</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.2873039116744009</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>5.2310374891012125E-2</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
+        <v>2.632068528911268</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>1.7436791630343982E-2</v>
       </c>
-      <c r="H9">
+      <c r="J9">
+        <v>-2.5065063027844241</v>
+      </c>
+      <c r="K9">
+        <v>0.4359197907585004</v>
+      </c>
+      <c r="L9">
+        <v>0.7497820401046128</v>
+      </c>
+      <c r="M9">
+        <v>12.27277779098997</v>
+      </c>
+      <c r="N9">
+        <v>0.61028770706190061</v>
+      </c>
+      <c r="O9">
+        <v>1.2554489973844891</v>
+      </c>
+      <c r="P9">
+        <v>-7.5863199382961515</v>
+      </c>
+      <c r="Q9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -908,22 +1142,49 @@
         <v>3.8095238095238133</v>
       </c>
       <c r="D10">
+        <v>-0.596750941291599</v>
+      </c>
+      <c r="E10">
         <v>0.1762114537444934</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.30864197530864196</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
+        <v>4.3926858063862229</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>0.2557319223985971</v>
       </c>
-      <c r="H10">
+      <c r="J10">
+        <v>-2.8145082838879762</v>
+      </c>
+      <c r="K10">
+        <v>0.70484581497797361</v>
+      </c>
+      <c r="L10">
+        <v>0.98765432098765826</v>
+      </c>
+      <c r="M10">
+        <v>4.632610054898449</v>
+      </c>
+      <c r="N10">
+        <v>1.0572687224669604</v>
+      </c>
+      <c r="O10">
+        <v>1.7019400352733645</v>
+      </c>
+      <c r="P10">
+        <v>9.9918194392969379</v>
+      </c>
+      <c r="Q10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -934,22 +1195,49 @@
         <v>3.7472845763939056</v>
       </c>
       <c r="D11">
+        <v>-6.7979974980993241</v>
+      </c>
+      <c r="E11">
         <v>9.0334236675700091E-2</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.33490224475018515</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
+        <v>-12.161806903724678</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0.11766835626357301</v>
       </c>
-      <c r="H11">
+      <c r="J11">
+        <v>-10.302647966237464</v>
+      </c>
+      <c r="K11">
+        <v>0.90334236675700086</v>
+      </c>
+      <c r="L11">
+        <v>1.2943519188993442</v>
+      </c>
+      <c r="M11">
+        <v>-2.9212117267898656</v>
+      </c>
+      <c r="N11">
+        <v>1.8970189701897018</v>
+      </c>
+      <c r="O11">
+        <v>2.5706010137581341</v>
+      </c>
+      <c r="P11">
+        <v>6.7924379251299376</v>
+      </c>
+      <c r="Q11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -960,22 +1248,49 @@
         <v>2.3027968514486687</v>
       </c>
       <c r="D12">
+        <v>-5.5179393927184304</v>
+      </c>
+      <c r="E12">
         <v>0.333889816360601</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.24284039524368536</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
+        <v>-12.650096637024841</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>0.13398090772066121</v>
       </c>
-      <c r="H12">
+      <c r="J12">
+        <v>-5.0464432869085902</v>
+      </c>
+      <c r="K12">
+        <v>0.8347245409015025</v>
+      </c>
+      <c r="L12">
+        <v>0.87924970691676441</v>
+      </c>
+      <c r="M12">
+        <v>-15.23109959694103</v>
+      </c>
+      <c r="N12">
+        <v>1.335559265442404</v>
+      </c>
+      <c r="O12">
+        <v>1.6915089599732074</v>
+      </c>
+      <c r="P12">
+        <v>-7.5809706590813448</v>
+      </c>
+      <c r="Q12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -986,22 +1301,49 @@
         <v>6.2980883636075262</v>
       </c>
       <c r="D13">
+        <v>6.8811234085417725</v>
+      </c>
+      <c r="E13">
         <v>0.94711917916337818</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.77734591893392191</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
+        <v>10.10420428516159</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>0.11104941699056801</v>
       </c>
-      <c r="H13">
+      <c r="J13">
+        <v>2.1572739074119398</v>
+      </c>
+      <c r="K13">
+        <v>0.55248618784530379</v>
+      </c>
+      <c r="L13">
+        <v>1.1977472832553451</v>
+      </c>
+      <c r="M13">
+        <v>9.942256962660915</v>
+      </c>
+      <c r="N13">
+        <v>0.94711917916337818</v>
+      </c>
+      <c r="O13">
+        <v>3.3076862060759931</v>
+      </c>
+      <c r="P13">
+        <v>6.8408315935823332</v>
+      </c>
+      <c r="Q13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1012,22 +1354,49 @@
         <v>3.7019898195279968</v>
       </c>
       <c r="D14">
+        <v>-4.7619764312761621</v>
+      </c>
+      <c r="E14">
         <v>0.53763440860215062</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.35477402437142597</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
+        <v>-7.9923345786100342</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>0.10026222427887974</v>
       </c>
-      <c r="H14">
+      <c r="J14">
+        <v>-8.9064663078612458</v>
+      </c>
+      <c r="K14">
+        <v>0.38402457757296465</v>
+      </c>
+      <c r="L14">
+        <v>0.91778497609130527</v>
+      </c>
+      <c r="M14">
+        <v>2.8005710398186929</v>
+      </c>
+      <c r="N14">
+        <v>1.3056835637480799</v>
+      </c>
+      <c r="O14">
+        <v>1.8432824309733045</v>
+      </c>
+      <c r="P14">
+        <v>2.0941236614853151</v>
+      </c>
+      <c r="Q14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1038,22 +1407,49 @@
         <v>2.4157384637639132</v>
       </c>
       <c r="D15">
+        <v>-3.4970825904461496</v>
+      </c>
+      <c r="E15">
         <v>0.72202166064981954</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.82453348763198797</v>
       </c>
-      <c r="F15">
+      <c r="G15">
+        <v>-5.1501839801606923</v>
+      </c>
+      <c r="H15">
         <v>0.28880866425992779</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>0.20974974685374395</v>
       </c>
-      <c r="H15">
+      <c r="J15">
+        <v>-15.912820435833952</v>
+      </c>
+      <c r="K15">
+        <v>1.2996389891696751</v>
+      </c>
+      <c r="L15">
+        <v>1.3235932301460984</v>
+      </c>
+      <c r="M15">
+        <v>-10.479340258629303</v>
+      </c>
+      <c r="N15">
+        <v>1.4440433212996391</v>
+      </c>
+      <c r="O15">
+        <v>1.9456097208158445</v>
+      </c>
+      <c r="P15">
+        <v>5.8283080477092168</v>
+      </c>
+      <c r="Q15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1064,22 +1460,49 @@
         <v>2.186551774930023</v>
       </c>
       <c r="D16">
+        <v>-9.2165675009593961</v>
+      </c>
+      <c r="E16">
         <v>7.3260073260073263E-2</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
+        <v>-6.8341885157707587</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>1.4729709824719803E-2</v>
       </c>
-      <c r="H16">
+      <c r="J16">
+        <v>-6.385924297836433</v>
+      </c>
+      <c r="K16">
+        <v>1.2454212454212454</v>
+      </c>
+      <c r="L16">
+        <v>1.0531742524672232</v>
+      </c>
+      <c r="M16">
+        <v>-5.5678181173495238</v>
+      </c>
+      <c r="N16">
+        <v>1.9047619047619049</v>
+      </c>
+      <c r="O16">
+        <v>1.6791869200176723</v>
+      </c>
+      <c r="P16">
+        <v>-3.6369304947008261</v>
+      </c>
+      <c r="Q16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1090,22 +1513,49 @@
         <v>7.2874795295518897</v>
       </c>
       <c r="D17">
+        <v>5.6331939059858289</v>
+      </c>
+      <c r="E17">
         <v>0.29673590504451042</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.23075777877029449</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="G17">
-        <v>0</v>
+        <v>12.658630290073871</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-5.9551797305877026</v>
+      </c>
+      <c r="K17">
+        <v>0.89020771513353114</v>
+      </c>
+      <c r="L17">
+        <v>1.3398838767306833</v>
+      </c>
+      <c r="M17">
+        <v>-6.5088183810762743</v>
+      </c>
+      <c r="N17">
+        <v>1.3353115727002967</v>
+      </c>
+      <c r="O17">
+        <v>3.2827154979901843</v>
+      </c>
+      <c r="P17">
+        <v>-3.1673541985173999</v>
+      </c>
+      <c r="Q17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1116,22 +1566,49 @@
         <v>2.6597241767520372</v>
       </c>
       <c r="D18">
+        <v>0.88439343653293134</v>
+      </c>
+      <c r="E18">
         <v>0.35161744022503516</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.41514213340839368</v>
       </c>
-      <c r="F18">
+      <c r="G18">
+        <v>-4.1732103572456349</v>
+      </c>
+      <c r="H18">
         <v>7.0323488045007029E-2</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>8.4435688150861637E-2</v>
       </c>
-      <c r="H18">
+      <c r="J18">
+        <v>-4.2314518509305543</v>
+      </c>
+      <c r="K18">
+        <v>0.9142053445850914</v>
+      </c>
+      <c r="L18">
+        <v>1.2243174781874537</v>
+      </c>
+      <c r="M18">
+        <v>-7.6139614033196485</v>
+      </c>
+      <c r="N18">
+        <v>1.4064697609001406</v>
+      </c>
+      <c r="O18">
+        <v>1.7520405291303189</v>
+      </c>
+      <c r="P18">
+        <v>-6.9415212603896315</v>
+      </c>
+      <c r="Q18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1142,22 +1619,49 @@
         <v>4.1259914582062338</v>
       </c>
       <c r="D19">
+        <v>-11.421945937086569</v>
+      </c>
+      <c r="E19">
         <v>7.621951219512195E-2</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>3.8133007931665644E-2</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
+        <v>-14.253764513671827</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>0.22117144600366767</v>
       </c>
-      <c r="H19">
+      <c r="J19">
+        <v>-13.331889012061518</v>
+      </c>
+      <c r="K19">
+        <v>0.3048780487804878</v>
+      </c>
+      <c r="L19">
+        <v>0.50335570469799695</v>
+      </c>
+      <c r="M19">
+        <v>-12.829678390385247</v>
+      </c>
+      <c r="N19">
+        <v>0.68597560975609762</v>
+      </c>
+      <c r="O19">
+        <v>1.4032946918853029</v>
+      </c>
+      <c r="P19">
+        <v>-6.1832995002951838</v>
+      </c>
+      <c r="Q19">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1168,22 +1672,49 @@
         <v>4.7593293672255204</v>
       </c>
       <c r="D20">
+        <v>-15.756015257869171</v>
+      </c>
+      <c r="E20">
         <v>0.54012345679012341</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.92714208452445346</v>
       </c>
-      <c r="F20">
+      <c r="G20">
+        <v>-11.440617383593224</v>
+      </c>
+      <c r="H20">
         <v>7.716049382716049E-2</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>0.10044039249014561</v>
       </c>
-      <c r="H20">
+      <c r="J20">
+        <v>-15.297949876224292</v>
+      </c>
+      <c r="K20">
+        <v>1.0802469135802468</v>
+      </c>
+      <c r="L20">
+        <v>1.5993200958046856</v>
+      </c>
+      <c r="M20">
+        <v>7.0578730750079393</v>
+      </c>
+      <c r="N20">
+        <v>2.0061728395061729</v>
+      </c>
+      <c r="O20">
+        <v>2.4492003399521014</v>
+      </c>
+      <c r="P20">
+        <v>6.2493275903146506</v>
+      </c>
+      <c r="Q20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1194,22 +1725,49 @@
         <v>4.932699920823433</v>
       </c>
       <c r="D21">
+        <v>-6.3384132368504584E-2</v>
+      </c>
+      <c r="E21">
         <v>0.63041765169424746</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.43547110055423599</v>
       </c>
-      <c r="F21">
+      <c r="G21">
+        <v>-7.0170493606473094</v>
+      </c>
+      <c r="H21">
         <v>0.2364066193853428</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>0.11084718923199453</v>
       </c>
-      <c r="H21">
+      <c r="J21">
+        <v>-10.04582048560043</v>
+      </c>
+      <c r="K21">
+        <v>1.4972419227738378</v>
+      </c>
+      <c r="L21">
+        <v>1.6864608076009466</v>
+      </c>
+      <c r="M21">
+        <v>-5.8827119042837781</v>
+      </c>
+      <c r="N21">
+        <v>2.9156816390858946</v>
+      </c>
+      <c r="O21">
+        <v>2.9216152019002446</v>
+      </c>
+      <c r="P21">
+        <v>7.1625513706292461</v>
+      </c>
+      <c r="Q21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1220,22 +1778,49 @@
         <v>3.8976148923793001</v>
       </c>
       <c r="D22">
+        <v>6.8853289052918196</v>
+      </c>
+      <c r="E22">
         <v>0.5079825834542816</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.4072134962187417</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
       <c r="G22">
+        <v>1.5542014169046383</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>7.9988365328689387E-2</v>
       </c>
-      <c r="H22">
+      <c r="J22">
+        <v>-3.5349680306595506</v>
+      </c>
+      <c r="K22">
+        <v>0.94339622641509435</v>
+      </c>
+      <c r="L22">
+        <v>1.199825479930192</v>
+      </c>
+      <c r="M22">
+        <v>-5.9029539121625136</v>
+      </c>
+      <c r="N22">
+        <v>1.6690856313497822</v>
+      </c>
+      <c r="O22">
+        <v>2.1960442117510213</v>
+      </c>
+      <c r="P22">
+        <v>9.5620106901822037</v>
+      </c>
+      <c r="Q22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1246,22 +1831,49 @@
         <v>6.3297455271224017</v>
       </c>
       <c r="D23">
+        <v>0.55397467702275893</v>
+      </c>
+      <c r="E23">
         <v>0.78125</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.66291253831350638</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
       <c r="G23">
+        <v>-8.3511298572747474</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>-4.2768550858928576E-2</v>
       </c>
-      <c r="H23">
+      <c r="J23">
+        <v>-11.307234262258472</v>
+      </c>
+      <c r="K23">
+        <v>1.0653409090909089</v>
+      </c>
+      <c r="L23">
+        <v>1.3115688930073484</v>
+      </c>
+      <c r="M23">
+        <v>-5.7233617025268524</v>
+      </c>
+      <c r="N23">
+        <v>3.3380681818181817</v>
+      </c>
+      <c r="O23">
+        <v>3.7493762919666502</v>
+      </c>
+      <c r="P23">
+        <v>6.4738432989031143</v>
+      </c>
+      <c r="Q23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1272,22 +1884,49 @@
         <v>4.5317220543806647</v>
       </c>
       <c r="D24">
+        <v>4.3985694433532263</v>
+      </c>
+      <c r="E24">
         <v>0.68540095956134339</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.67975830815710592</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
       <c r="G24">
+        <v>3.0592690321141678</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>0.32271354023620197</v>
       </c>
-      <c r="H24">
+      <c r="J24">
+        <v>-2.9943746100638822</v>
+      </c>
+      <c r="K24">
+        <v>1.0966415352981496</v>
+      </c>
+      <c r="L24">
+        <v>1.3320516341664439</v>
+      </c>
+      <c r="M24">
+        <v>4.4405883786528335</v>
+      </c>
+      <c r="N24">
+        <v>2.2618231665524333</v>
+      </c>
+      <c r="O24">
+        <v>2.8288931612194483</v>
+      </c>
+      <c r="P24">
+        <v>-8.0975912432745183</v>
+      </c>
+      <c r="Q24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1298,22 +1937,49 @@
         <v>3.0468599344346656</v>
       </c>
       <c r="D25">
+        <v>7.4857926372429606</v>
+      </c>
+      <c r="E25">
         <v>0.70512820512820518</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.84206466542393366</v>
       </c>
-      <c r="F25">
+      <c r="G25">
+        <v>-13.236836793000403</v>
+      </c>
+      <c r="H25">
         <v>0.19230769230769232</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>0.28283087998972106</v>
       </c>
-      <c r="H25">
+      <c r="J25">
+        <v>-6.6078860319447763</v>
+      </c>
+      <c r="K25">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L25">
+        <v>1.3884425017677016</v>
+      </c>
+      <c r="M25">
+        <v>10.916239162889724</v>
+      </c>
+      <c r="N25">
+        <v>2.0512820512820511</v>
+      </c>
+      <c r="O25">
+        <v>2.1083756508324196</v>
+      </c>
+      <c r="P25">
+        <v>7.0580075039952019</v>
+      </c>
+      <c r="Q25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1324,22 +1990,49 @@
         <v>2.8486076611321725</v>
       </c>
       <c r="D26">
+        <v>-5.7222460944992548</v>
+      </c>
+      <c r="E26">
         <v>0.45691906005221933</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.50987057131650892</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
       <c r="G26">
+        <v>3.1186180342564538</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>-1.9610406589093642E-2</v>
       </c>
-      <c r="H26">
+      <c r="J26">
+        <v>-9.7956932980359106</v>
+      </c>
+      <c r="K26">
+        <v>1.1749347258485638</v>
+      </c>
+      <c r="L26">
+        <v>1.4642436919858717</v>
+      </c>
+      <c r="M26">
+        <v>9.026776949684395</v>
+      </c>
+      <c r="N26">
+        <v>1.5013054830287207</v>
+      </c>
+      <c r="O26">
+        <v>1.660347757876838</v>
+      </c>
+      <c r="P26">
+        <v>7.4830463669658345</v>
+      </c>
+      <c r="Q26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1350,22 +2043,49 @@
         <v>8.436719317956511</v>
       </c>
       <c r="D27">
+        <v>5.1933249114319802</v>
+      </c>
+      <c r="E27">
         <v>0.33025099075297226</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.38992796246116346</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
       <c r="G27">
+        <v>-5.1632993911107121</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>0.34366532284712303</v>
       </c>
-      <c r="H27">
+      <c r="J27">
+        <v>-7.0470436128986043</v>
+      </c>
+      <c r="K27">
+        <v>1.1228533685601056</v>
+      </c>
+      <c r="L27">
+        <v>2.1346903707620086</v>
+      </c>
+      <c r="M27">
+        <v>6.8102594059329977</v>
+      </c>
+      <c r="N27">
+        <v>2.7741083223249667</v>
+      </c>
+      <c r="O27">
+        <v>3.7671006542859033</v>
+      </c>
+      <c r="P27">
+        <v>10.01607375480596</v>
+      </c>
+      <c r="Q27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1376,22 +2096,49 @@
         <v>2.99270528087786</v>
       </c>
       <c r="D28">
+        <v>11.505293567875709</v>
+      </c>
+      <c r="E28">
         <v>0.6840796019900498</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.69206309620301365</v>
       </c>
-      <c r="F28" s="3">
+      <c r="G28">
+        <v>0.13838696509912285</v>
+      </c>
+      <c r="H28">
         <v>-6.2189054726368161E-2</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>-0.11222644803291693</v>
       </c>
-      <c r="H28">
+      <c r="J28">
+        <v>-3.6279017953722001</v>
+      </c>
+      <c r="K28">
+        <v>1.2437810945273633</v>
+      </c>
+      <c r="L28">
+        <v>1.4215350084169949</v>
+      </c>
+      <c r="M28">
+        <v>9.8444154907075294</v>
+      </c>
+      <c r="N28">
+        <v>1.8656716417910446</v>
+      </c>
+      <c r="O28">
+        <v>2.0200760645925615</v>
+      </c>
+      <c r="P28">
+        <v>-12.213415359593551</v>
+      </c>
+      <c r="Q28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1402,22 +2149,49 @@
         <v>5.1259299706504624</v>
       </c>
       <c r="D29">
+        <v>15.596293217680183</v>
+      </c>
+      <c r="E29">
         <v>0.20422055820285909</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.10920756262370548</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
       <c r="G29">
+        <v>-3.7069892311157306</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <v>8.1905671967771349E-2</v>
       </c>
-      <c r="H29">
+      <c r="J29">
+        <v>-4.0884490039494503</v>
+      </c>
+      <c r="K29">
+        <v>0.6807351940095302</v>
+      </c>
+      <c r="L29">
+        <v>0.58016517643846832</v>
+      </c>
+      <c r="M29">
+        <v>6.1965079985969531</v>
+      </c>
+      <c r="N29">
+        <v>1.0891763104152483</v>
+      </c>
+      <c r="O29">
+        <v>1.5766841853798312</v>
+      </c>
+      <c r="P29">
+        <v>4.8161157819453475</v>
+      </c>
+      <c r="Q29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1428,22 +2202,49 @@
         <v>5.1565897915368186</v>
       </c>
       <c r="D30">
+        <v>19.716088808637398</v>
+      </c>
+      <c r="E30">
         <v>0.89841050449205251</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>1.0180760440473748</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
       <c r="G30">
+        <v>8.6713823193924799</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>4.8479811621306559E-2</v>
       </c>
-      <c r="H30">
+      <c r="J30">
+        <v>-14.259095605099152</v>
+      </c>
+      <c r="K30">
+        <v>1.3130615065653075</v>
+      </c>
+      <c r="L30">
+        <v>1.516725535009356</v>
+      </c>
+      <c r="M30">
+        <v>9.1030719188958802</v>
+      </c>
+      <c r="N30">
+        <v>1.5894955079474777</v>
+      </c>
+      <c r="O30">
+        <v>2.3201052704480918</v>
+      </c>
+      <c r="P30">
+        <v>3.8000446032709099</v>
+      </c>
+      <c r="Q30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1454,22 +2255,49 @@
         <v>5.4780033840947571</v>
       </c>
       <c r="D31">
+        <v>-14.647403324241223</v>
+      </c>
+      <c r="E31">
         <v>0.98383696416022481</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.88127467569091933</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31">
+        <v>-5.0108165053779432</v>
+      </c>
+      <c r="H31">
         <v>-7.0274068868587489E-2</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>2.1150592216594887E-2</v>
       </c>
-      <c r="H31">
+      <c r="J31">
+        <v>3.6332620692882345</v>
+      </c>
+      <c r="K31">
+        <v>1.5460295151089247</v>
+      </c>
+      <c r="L31">
+        <v>1.9176536943034437</v>
+      </c>
+      <c r="M31">
+        <v>-7.7266041771547851</v>
+      </c>
+      <c r="N31">
+        <v>3.0217849613492622</v>
+      </c>
+      <c r="O31">
+        <v>3.5815002820079087</v>
+      </c>
+      <c r="P31">
+        <v>-9.5654279465288639</v>
+      </c>
+      <c r="Q31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1480,22 +2308,49 @@
         <v>4.3745545030892075</v>
       </c>
       <c r="D32">
+        <v>-0.13447495679283381</v>
+      </c>
+      <c r="E32">
         <v>0.45016077170418006</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.60754842245844565</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
       <c r="G32">
+        <v>5.7300374430574719</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <v>0.17009297214952776</v>
       </c>
-      <c r="H32">
+      <c r="J32">
+        <v>-5.6821824731442145</v>
+      </c>
+      <c r="K32">
+        <v>1.4790996784565917</v>
+      </c>
+      <c r="L32">
+        <v>1.7912514056472959</v>
+      </c>
+      <c r="M32">
+        <v>2.2387483329778277</v>
+      </c>
+      <c r="N32">
+        <v>2.1864951768488745</v>
+      </c>
+      <c r="O32">
+        <v>2.936355378514762</v>
+      </c>
+      <c r="P32">
+        <v>9.0602090551519314</v>
+      </c>
+      <c r="Q32">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1506,22 +2361,49 @@
         <v>1.4083621502672172</v>
       </c>
       <c r="D33">
+        <v>8.1843942822455329</v>
+      </c>
+      <c r="E33">
         <v>0.25141420490257699</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.30179188934297108</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33">
+        <v>-5.2291264226973455</v>
+      </c>
+      <c r="H33">
         <v>-6.2853551225644247E-2</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>6.2873310279729054E-3</v>
       </c>
-      <c r="H33">
+      <c r="J33">
+        <v>-16.722124205329113</v>
+      </c>
+      <c r="K33">
+        <v>0.37712130735386551</v>
+      </c>
+      <c r="L33">
+        <v>0.48412448915435685</v>
+      </c>
+      <c r="M33">
+        <v>6.3957642664667249</v>
+      </c>
+      <c r="N33">
+        <v>0.62853551225644255</v>
+      </c>
+      <c r="O33">
+        <v>0.67274441999371548</v>
+      </c>
+      <c r="P33">
+        <v>2.3138303064524992</v>
+      </c>
+      <c r="Q33">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1532,22 +2414,49 @@
         <v>1.7912869804019502</v>
       </c>
       <c r="D34">
+        <v>13.668027873572145</v>
+      </c>
+      <c r="E34">
         <v>0.56109725685785539</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.56796904256647962</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>8.7666693593292191</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>2.4965672200729677E-2</v>
       </c>
-      <c r="H34">
+      <c r="J34">
+        <v>-11.889360016122993</v>
+      </c>
+      <c r="K34">
+        <v>0.74812967581047385</v>
+      </c>
+      <c r="L34">
+        <v>0.78641867432281465</v>
+      </c>
+      <c r="M34">
+        <v>-8.4831980475598332</v>
+      </c>
+      <c r="N34">
+        <v>0.81047381546134667</v>
+      </c>
+      <c r="O34">
+        <v>1.0423168143802299</v>
+      </c>
+      <c r="P34">
+        <v>7.2092090336702315</v>
+      </c>
+      <c r="Q34">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1558,22 +2467,49 @@
         <v>0.46855733662144938</v>
       </c>
       <c r="D35">
+        <v>5.9025711802153022</v>
+      </c>
+      <c r="E35">
         <v>0.12330456226880394</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.15413070283600494</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
       <c r="G35">
-        <v>0</v>
+        <v>11.742136731725555</v>
       </c>
       <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.8286149188104697</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0.23427866831072469</v>
+      </c>
+      <c r="M35">
+        <v>6.191358229947598</v>
+      </c>
+      <c r="N35">
+        <v>0.18495684340320592</v>
+      </c>
+      <c r="O35">
+        <v>0.30209617755857526</v>
+      </c>
+      <c r="P35">
+        <v>8.9155609121265744</v>
+      </c>
+      <c r="Q35">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1584,22 +2520,49 @@
         <v>1.1575484342634337</v>
       </c>
       <c r="D36">
+        <v>12.111628408626251</v>
+      </c>
+      <c r="E36">
         <v>0.30432136335970783</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.30461800901669306</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
       <c r="G36">
+        <v>-3.8584641976584524</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
         <v>-3.0461800901669302E-2</v>
       </c>
-      <c r="H36">
+      <c r="J36">
+        <v>-1.1653995142566942</v>
+      </c>
+      <c r="K36">
+        <v>0.60864272671941566</v>
+      </c>
+      <c r="L36">
+        <v>0.61532837821372832</v>
+      </c>
+      <c r="M36">
+        <v>7.8930101597270559</v>
+      </c>
+      <c r="N36">
+        <v>0.66950699939135727</v>
+      </c>
+      <c r="O36">
+        <v>0.76763738272207482</v>
+      </c>
+      <c r="P36">
+        <v>3.8587826331061419</v>
+      </c>
+      <c r="Q36">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1610,22 +2573,49 @@
         <v>1.4921766447169724</v>
       </c>
       <c r="D37">
+        <v>-16.697267579755888</v>
+      </c>
+      <c r="E37">
         <v>0.42245021122510562</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.43496647133450406</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
       <c r="G37">
+        <v>-5.8502471872364756</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
         <v>6.0412009907514679E-3</v>
       </c>
-      <c r="H37">
+      <c r="J37">
+        <v>-5.32132962214994</v>
+      </c>
+      <c r="K37">
+        <v>0.6035003017501509</v>
+      </c>
+      <c r="L37">
+        <v>0.79743853077992188</v>
+      </c>
+      <c r="M37">
+        <v>-6.7105234072069582</v>
+      </c>
+      <c r="N37">
+        <v>0.96560048280024147</v>
+      </c>
+      <c r="O37">
+        <v>1.1357457862623064</v>
+      </c>
+      <c r="P37">
+        <v>-3.6272069117730092</v>
+      </c>
+      <c r="Q37">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1636,22 +2626,49 @@
         <v>0.61094964114124095</v>
       </c>
       <c r="D38">
+        <v>3.0838729997370953</v>
+      </c>
+      <c r="E38">
         <v>0.23710729104919975</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.19574114716176413</v>
       </c>
-      <c r="F38">
+      <c r="G38">
+        <v>-11.397401499422452</v>
+      </c>
+      <c r="H38">
         <v>5.9276822762299938E-2</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>2.37261996559755E-2</v>
       </c>
-      <c r="H38">
+      <c r="J38">
+        <v>-14.303772506700108</v>
+      </c>
+      <c r="K38">
+        <v>0.29638411381149971</v>
+      </c>
+      <c r="L38">
+        <v>0.34996144492556441</v>
+      </c>
+      <c r="M38">
+        <v>0.64246147772970785</v>
+      </c>
+      <c r="N38">
+        <v>0.41493775933609961</v>
+      </c>
+      <c r="O38">
+        <v>0.42707159380746451</v>
+      </c>
+      <c r="P38">
+        <v>-6.4965559301814135</v>
+      </c>
+      <c r="Q38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1662,22 +2679,49 @@
         <v>1.7781908302354428</v>
       </c>
       <c r="D39">
+        <v>3.5680179716747937</v>
+      </c>
+      <c r="E39">
         <v>0.18575851393188852</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.16109045848822237</v>
       </c>
-      <c r="F39">
+      <c r="G39">
+        <v>-7.8800845791229852</v>
+      </c>
+      <c r="H39">
         <v>6.1919504643962855E-2</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>6.1957868649262114E-3</v>
       </c>
-      <c r="H39">
+      <c r="J39">
+        <v>-1.221181346349844</v>
+      </c>
+      <c r="K39">
+        <v>0.43343653250773995</v>
+      </c>
+      <c r="L39">
+        <v>0.65055762081784385</v>
+      </c>
+      <c r="M39">
+        <v>7.7899149653699995</v>
+      </c>
+      <c r="N39">
+        <v>0.86687306501547989</v>
+      </c>
+      <c r="O39">
+        <v>1.0656753407682804</v>
+      </c>
+      <c r="P39">
+        <v>-4.5104097222836605</v>
+      </c>
+      <c r="Q39">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1688,22 +2732,49 @@
         <v>1.5250139482983021</v>
       </c>
       <c r="D40">
+        <v>8.9790150251121172</v>
+      </c>
+      <c r="E40">
         <v>0.30978934324659235</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.40295083999752035</v>
       </c>
-      <c r="F40" s="3">
+      <c r="G40">
+        <v>-9.0359315879678359</v>
+      </c>
+      <c r="H40">
         <v>-6.1957868649318466E-2</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>2.4796974769069717E-2</v>
       </c>
-      <c r="H40">
+      <c r="J40">
+        <v>-16.803243931517777</v>
+      </c>
+      <c r="K40">
+        <v>0.55762081784386619</v>
+      </c>
+      <c r="L40">
+        <v>0.77490546153369289</v>
+      </c>
+      <c r="M40">
+        <v>0.8158731216279882</v>
+      </c>
+      <c r="N40">
+        <v>0.86741016109045854</v>
+      </c>
+      <c r="O40">
+        <v>0.97948050337858505</v>
+      </c>
+      <c r="P40">
+        <v>-11.09704510642824</v>
+      </c>
+      <c r="Q40">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1714,22 +2785,49 @@
         <v>1.8035824583075999</v>
       </c>
       <c r="D41">
+        <v>15.097945560687659</v>
+      </c>
+      <c r="E41">
         <v>0.55487053020961774</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.49413218035824585</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41">
+        <v>11.726102643648986</v>
+      </c>
+      <c r="H41">
         <v>-6.1652281134401972E-2</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>9.2649783817171094E-2</v>
       </c>
-      <c r="H41">
+      <c r="J41">
+        <v>-3.5335474027770717</v>
+      </c>
+      <c r="K41">
+        <v>0.73982737361282369</v>
+      </c>
+      <c r="L41">
+        <v>0.87090796788140268</v>
+      </c>
+      <c r="M41">
+        <v>-11.240227616080047</v>
+      </c>
+      <c r="N41">
+        <v>1.1097410604192355</v>
+      </c>
+      <c r="O41">
+        <v>1.1612106238418749</v>
+      </c>
+      <c r="P41">
+        <v>4.3096829248015807</v>
+      </c>
+      <c r="Q41">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1740,22 +2838,49 @@
         <v>1.1484576994768751</v>
       </c>
       <c r="D42">
+        <v>14.726766862663659</v>
+      </c>
+      <c r="E42">
         <v>0.24038461538461539</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.30665624436293121</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
       <c r="G42">
+        <v>-16.568652201558255</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>3.6077205219163556E-2</v>
       </c>
-      <c r="H42">
+      <c r="J42">
+        <v>-8.4350693181049792</v>
+      </c>
+      <c r="K42">
+        <v>0.42067307692307693</v>
+      </c>
+      <c r="L42">
+        <v>0.61932535626239882</v>
+      </c>
+      <c r="M42">
+        <v>11.391563114886665</v>
+      </c>
+      <c r="N42">
+        <v>0.72115384615384615</v>
+      </c>
+      <c r="O42">
+        <v>0.84781432265046663</v>
+      </c>
+      <c r="P42">
+        <v>-4.0289194107783155</v>
+      </c>
+      <c r="Q42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1766,22 +2891,49 @@
         <v>1.4120879120879146</v>
       </c>
       <c r="D43">
+        <v>-13.903159431616302</v>
+      </c>
+      <c r="E43">
         <v>0.3844041735310269</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.41208791208791212</v>
       </c>
-      <c r="F43">
+      <c r="G43">
+        <v>-17.847072638372772</v>
+      </c>
+      <c r="H43">
         <v>0.10982976386600769</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>0.12637362637362387</v>
       </c>
-      <c r="H43">
+      <c r="J43">
+        <v>-7.3902888115593992</v>
+      </c>
+      <c r="K43">
+        <v>0.60406370126304221</v>
+      </c>
+      <c r="L43">
+        <v>0.59890109890110388</v>
+      </c>
+      <c r="M43">
+        <v>10.601016596254194</v>
+      </c>
+      <c r="N43">
+        <v>0.65897858319604619</v>
+      </c>
+      <c r="O43">
+        <v>0.80769230769231015</v>
+      </c>
+      <c r="P43">
+        <v>-6.3742995678274781</v>
+      </c>
+      <c r="Q43">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1792,22 +2944,49 @@
         <v>1.472906136203062</v>
       </c>
       <c r="D44">
+        <v>-14.008027250924243</v>
+      </c>
+      <c r="E44">
         <v>0.48859934853420189</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.47285178542312323</v>
       </c>
-      <c r="F44">
+      <c r="G44">
+        <v>13.529853560408741</v>
+      </c>
+      <c r="H44">
         <v>5.428881650380022E-2</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>5.978585792706867E-2</v>
       </c>
-      <c r="H44">
+      <c r="J44">
+        <v>-3.0420372104137248</v>
+      </c>
+      <c r="K44">
+        <v>0.65146579804560267</v>
+      </c>
+      <c r="L44">
+        <v>0.78265123104517031</v>
+      </c>
+      <c r="M44">
+        <v>0.79526693548078942</v>
+      </c>
+      <c r="N44">
+        <v>1.0857763300760044</v>
+      </c>
+      <c r="O44">
+        <v>1.1685417685743791</v>
+      </c>
+      <c r="P44">
+        <v>13.132265219073672</v>
+      </c>
+      <c r="Q44">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1818,22 +2997,49 @@
         <v>0.69690146885386506</v>
       </c>
       <c r="D45">
+        <v>-9.6982221925526932</v>
+      </c>
+      <c r="E45">
         <v>0.10718113612004287</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.19298809906723149</v>
       </c>
-      <c r="F45">
+      <c r="G45">
+        <v>12.421051899210751</v>
+      </c>
+      <c r="H45">
         <v>5.3590568060021437E-2</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>2.6803902648225582E-2</v>
       </c>
-      <c r="H45">
+      <c r="J45">
+        <v>2.2284840379088635</v>
+      </c>
+      <c r="K45">
+        <v>0.32154340836012862</v>
+      </c>
+      <c r="L45">
+        <v>0.3270076123083594</v>
+      </c>
+      <c r="M45">
+        <v>1.0965986284984379</v>
+      </c>
+      <c r="N45">
+        <v>0.32154340836012862</v>
+      </c>
+      <c r="O45">
+        <v>0.38061541760481055</v>
+      </c>
+      <c r="P45">
+        <v>6.0265291537021835</v>
+      </c>
+      <c r="Q45">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1844,22 +3050,49 @@
         <v>1.3701528857853178</v>
       </c>
       <c r="D46">
+        <v>1.9420120314899936</v>
+      </c>
+      <c r="E46">
         <v>0.31712473572938688</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.38618208749933636</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
       <c r="G46">
+        <v>-4.4153672987093762</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>4.2321324657459372E-2</v>
       </c>
-      <c r="H46">
+      <c r="J46">
+        <v>3.6093260937033378</v>
+      </c>
+      <c r="K46">
+        <v>0.63424947145877375</v>
+      </c>
+      <c r="L46">
+        <v>0.67185102893720816</v>
+      </c>
+      <c r="M46">
+        <v>1.997421987595831</v>
+      </c>
+      <c r="N46">
+        <v>0.73995771670190269</v>
+      </c>
+      <c r="O46">
+        <v>0.81997566523832188</v>
+      </c>
+      <c r="P46">
+        <v>11.483283302689959</v>
+      </c>
+      <c r="Q46">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1870,22 +3103,49 @@
         <v>2.1548117154811739</v>
       </c>
       <c r="D47">
+        <v>-8.8193209651258258</v>
+      </c>
+      <c r="E47">
         <v>0.41797283176593525</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.47071129707112974</v>
       </c>
-      <c r="F47">
+      <c r="G47">
+        <v>4.4536172831719689</v>
+      </c>
+      <c r="H47">
         <v>5.2246603970741906E-2</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>5.753138075313332E-2</v>
       </c>
-      <c r="H47">
+      <c r="J47">
+        <v>-3.3131407887344895</v>
+      </c>
+      <c r="K47">
+        <v>0.7836990595611284</v>
+      </c>
+      <c r="L47">
+        <v>0.87866108786610642</v>
+      </c>
+      <c r="M47">
+        <v>-2.7384204373394088</v>
+      </c>
+      <c r="N47">
+        <v>0.99268547544409613</v>
+      </c>
+      <c r="O47">
+        <v>1.7730125523012601</v>
+      </c>
+      <c r="P47">
+        <v>3.3001355475931589</v>
+      </c>
+      <c r="Q47">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1896,22 +3156,49 @@
         <v>0.65188379016528308</v>
       </c>
       <c r="D48">
+        <v>-15.582089211786998</v>
+      </c>
+      <c r="E48">
         <v>0.2052334530528476</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.21558361564521328</v>
       </c>
-      <c r="F48">
+      <c r="G48">
+        <v>-4.1745031303200673</v>
+      </c>
+      <c r="H48">
         <v>5.1308363263211899E-2</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>2.0531772918596189E-2</v>
       </c>
-      <c r="H48">
+      <c r="J48">
+        <v>-6.3702071927349735</v>
+      </c>
+      <c r="K48">
+        <v>0.35915854284248333</v>
+      </c>
+      <c r="L48">
+        <v>0.37983779899394782</v>
+      </c>
+      <c r="M48">
+        <v>0.25739882057454055</v>
+      </c>
+      <c r="N48">
+        <v>0.4104669061056952</v>
+      </c>
+      <c r="O48">
+        <v>0.45683194743866595</v>
+      </c>
+      <c r="P48">
+        <v>-3.6033700174317405</v>
+      </c>
+      <c r="Q48">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1922,22 +3209,49 @@
         <v>1.5619068279190942</v>
       </c>
       <c r="D49">
+        <v>16.609532852968847</v>
+      </c>
+      <c r="E49">
         <v>0.21680216802168023</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.24947122945930561</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
       <c r="G49">
+        <v>11.565041826981135</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
         <v>-3.2539725581642656E-2</v>
       </c>
-      <c r="H49">
+      <c r="J49">
+        <v>-1.4997110150489557</v>
+      </c>
+      <c r="K49">
+        <v>0.43360433604336046</v>
+      </c>
+      <c r="L49">
+        <v>0.52605889690330532</v>
+      </c>
+      <c r="M49">
+        <v>-0.48305565322009419</v>
+      </c>
+      <c r="N49">
+        <v>0.75880758807588078</v>
+      </c>
+      <c r="O49">
+        <v>0.98161505504637636</v>
+      </c>
+      <c r="P49">
+        <v>-13.777080803586836</v>
+      </c>
+      <c r="Q49">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1948,22 +3262,49 @@
         <v>1.6236402013313851</v>
       </c>
       <c r="D50">
+        <v>3.7466608106409551</v>
+      </c>
+      <c r="E50">
         <v>0.59459459459459463</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.52497699843048362</v>
       </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
       <c r="G50">
-        <v>0</v>
+        <v>-0.44838489566325129</v>
       </c>
       <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.22823185061928802</v>
+      </c>
+      <c r="K50">
+        <v>0.91891891891891886</v>
+      </c>
+      <c r="L50">
+        <v>0.94171131677220821</v>
+      </c>
+      <c r="M50">
+        <v>1.2688768987070893</v>
+      </c>
+      <c r="N50">
+        <v>0.91891891891891886</v>
+      </c>
+      <c r="O50">
+        <v>1.1473724089408479</v>
+      </c>
+      <c r="P50">
+        <v>5.5956698288194362</v>
+      </c>
+      <c r="Q50">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1974,22 +3315,49 @@
         <v>2.26360571520308</v>
       </c>
       <c r="D51">
+        <v>14.142065725319</v>
+      </c>
+      <c r="E51">
         <v>0.58729311265349704</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.4709156097821991</v>
       </c>
-      <c r="F51">
+      <c r="G51">
+        <v>-15.255532686181287</v>
+      </c>
+      <c r="H51">
         <v>0.10678056593699946</v>
       </c>
-      <c r="G51">
+      <c r="I51">
         <v>4.2810509980197704E-2</v>
       </c>
-      <c r="H51">
+      <c r="J51">
+        <v>-8.6627492518357805</v>
+      </c>
+      <c r="K51">
+        <v>0.96102509343299525</v>
+      </c>
+      <c r="L51">
+        <v>0.97393910204955547</v>
+      </c>
+      <c r="M51">
+        <v>6.2084196613607183</v>
+      </c>
+      <c r="N51">
+        <v>1.2279765082754939</v>
+      </c>
+      <c r="O51">
+        <v>1.2950179269010567</v>
+      </c>
+      <c r="P51">
+        <v>-13.563964769377154</v>
+      </c>
+      <c r="Q51">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -2000,22 +3368,49 @@
         <v>1.1251171997082983</v>
       </c>
       <c r="D52">
+        <v>-3.8096610704342089</v>
+      </c>
+      <c r="E52">
         <v>0.31233732431025507</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.31774143139909933</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
+        <v>5.1347793419975796</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
         <v>4.6879883321172183E-2</v>
       </c>
-      <c r="H52">
+      <c r="J52">
+        <v>-5.9960456711182397</v>
+      </c>
+      <c r="K52">
+        <v>0.52056220718375845</v>
+      </c>
+      <c r="L52">
+        <v>0.63548286279821053</v>
+      </c>
+      <c r="M52">
+        <v>-0.60189805957164455</v>
+      </c>
+      <c r="N52">
+        <v>0.72878709005726183</v>
+      </c>
+      <c r="O52">
+        <v>0.81779352015835216</v>
+      </c>
+      <c r="P52">
+        <v>7.7612446318419792</v>
+      </c>
+      <c r="Q52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -2026,22 +3421,49 @@
         <v>1.7352090583794846</v>
       </c>
       <c r="D53">
+        <v>6.3483765242788328</v>
+      </c>
+      <c r="E53">
         <v>0.2938295788442703</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.40684280182343779</v>
       </c>
-      <c r="F53">
+      <c r="G53">
+        <v>-9.943563126608451</v>
+      </c>
+      <c r="H53">
         <v>9.7943192948090105E-2</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>0.13234645360520653</v>
       </c>
-      <c r="H53">
+      <c r="J53">
+        <v>-14.020570766498658</v>
+      </c>
+      <c r="K53">
+        <v>0.44074436826640551</v>
+      </c>
+      <c r="L53">
+        <v>0.58820646046762415</v>
+      </c>
+      <c r="M53">
+        <v>6.8218405188069875</v>
+      </c>
+      <c r="N53">
+        <v>0.73457394711067581</v>
+      </c>
+      <c r="O53">
+        <v>0.79898044213518737</v>
+      </c>
+      <c r="P53">
+        <v>5.8015246603537785</v>
+      </c>
+      <c r="Q53">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -2052,22 +3474,49 @@
         <v>1.5766310393190457</v>
       </c>
       <c r="D54">
+        <v>15.056191331916033</v>
+      </c>
+      <c r="E54">
         <v>0.38666022232962782</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.45461140397541405</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
       <c r="G54">
+        <v>5.6723761528733538</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
         <v>7.2544372974802929E-2</v>
       </c>
-      <c r="H54">
+      <c r="J54">
+        <v>-11.590846146803178</v>
+      </c>
+      <c r="K54">
+        <v>0.53165780570323828</v>
+      </c>
+      <c r="L54">
+        <v>0.68191710596314314</v>
+      </c>
+      <c r="M54">
+        <v>6.9830619958867954</v>
+      </c>
+      <c r="N54">
+        <v>0.67665538907684875</v>
+      </c>
+      <c r="O54">
+        <v>0.95758572326738545</v>
+      </c>
+      <c r="P54">
+        <v>1.767122092040498</v>
+      </c>
+      <c r="Q54">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -2078,22 +3527,49 @@
         <v>0.61001763332222181</v>
       </c>
       <c r="D55">
+        <v>2.9089290250860151</v>
+      </c>
+      <c r="E55">
         <v>0.19056693663649357</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.24781966353716209</v>
       </c>
-      <c r="F55">
+      <c r="G55">
+        <v>-7.9193447985099734</v>
+      </c>
+      <c r="H55">
         <v>4.7641734159123393E-2</v>
       </c>
-      <c r="G55">
+      <c r="I55">
         <v>3.8126102082646995E-2</v>
       </c>
-      <c r="H55">
+      <c r="J55">
+        <v>-5.0603022716394293</v>
+      </c>
+      <c r="K55">
+        <v>0.28585040495474034</v>
+      </c>
+      <c r="L55">
+        <v>0.3050088166611109</v>
+      </c>
+      <c r="M55">
+        <v>0.18066561863655353</v>
+      </c>
+      <c r="N55">
+        <v>0.33349213911386372</v>
+      </c>
+      <c r="O55">
+        <v>0.37649525806605777</v>
+      </c>
+      <c r="P55">
+        <v>2.6861635034689675</v>
+      </c>
+      <c r="Q55">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2104,22 +3580,49 @@
         <v>1.4549209180081666</v>
       </c>
       <c r="D56">
+        <v>9.8265195114501136</v>
+      </c>
+      <c r="E56">
         <v>0.28142589118198874</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>0.39892992913127145</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
       <c r="G56">
+        <v>2.5000958507541813</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
         <v>0.1032524522457323</v>
       </c>
-      <c r="H56">
+      <c r="J56">
+        <v>2.0549918306131119</v>
+      </c>
+      <c r="K56">
+        <v>0.65666041275797382</v>
+      </c>
+      <c r="L56">
+        <v>0.75562021870746277</v>
+      </c>
+      <c r="M56">
+        <v>6.1617841732385932</v>
+      </c>
+      <c r="N56">
+        <v>0.70356472795497182</v>
+      </c>
+      <c r="O56">
+        <v>0.84479279110151606</v>
+      </c>
+      <c r="P56">
+        <v>7.9024707369895895</v>
+      </c>
+      <c r="Q56">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -2130,22 +3633,49 @@
         <v>2.2846043564722791</v>
       </c>
       <c r="D57">
+        <v>10.304021918013369</v>
+      </c>
+      <c r="E57">
         <v>0.46210720887245843</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>0.53646580030524726</v>
       </c>
-      <c r="F57">
+      <c r="G57">
+        <v>7.2644159802174162</v>
+      </c>
+      <c r="H57">
         <v>9.2421441774491686E-2</v>
       </c>
-      <c r="G57">
+      <c r="I57">
         <v>0.12486703972623006</v>
       </c>
-      <c r="H57">
+      <c r="J57">
+        <v>10.454680378183625</v>
+      </c>
+      <c r="K57">
+        <v>0.69316081330868762</v>
+      </c>
+      <c r="L57">
+        <v>0.94806456088424362</v>
+      </c>
+      <c r="M57">
+        <v>2.7932993155089241</v>
+      </c>
+      <c r="N57">
+        <v>0.92421441774491686</v>
+      </c>
+      <c r="O57">
+        <v>1.1654257041113754</v>
+      </c>
+      <c r="P57">
+        <v>0.99735831362949623</v>
+      </c>
+      <c r="Q57">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -2156,22 +3686,49 @@
         <v>0.87098530212303904</v>
       </c>
       <c r="D58">
+        <v>-20.366751646712629</v>
+      </c>
+      <c r="E58">
         <v>0.18140589569160998</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>0.2358918526583321</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
       <c r="G58">
+        <v>-7.0559393564579107</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
         <v>3.6291054255134361E-2</v>
       </c>
-      <c r="H58">
+      <c r="J58">
+        <v>-3.0327175393912991</v>
+      </c>
+      <c r="K58">
+        <v>0.22675736961451248</v>
+      </c>
+      <c r="L58">
+        <v>0.30393757938669352</v>
+      </c>
+      <c r="M58">
+        <v>-7.8259499646027617</v>
+      </c>
+      <c r="N58">
+        <v>0.36281179138321995</v>
+      </c>
+      <c r="O58">
+        <v>0.41734712393396262</v>
+      </c>
+      <c r="P58">
+        <v>0.21369368383529277</v>
+      </c>
+      <c r="Q58">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2182,22 +3739,49 @@
         <v>1.4829892410584538</v>
       </c>
       <c r="D59">
+        <v>-11.817353032052516</v>
+      </c>
+      <c r="E59">
         <v>0.24213075060532688</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>0.29562857419792132</v>
       </c>
-      <c r="F59">
+      <c r="G59">
+        <v>-9.1955560873077911</v>
+      </c>
+      <c r="H59">
         <v>4.8426150121065374E-2</v>
       </c>
-      <c r="G59">
+      <c r="I59">
         <v>1.4539110206464178E-2</v>
       </c>
-      <c r="H59">
+      <c r="J59">
+        <v>-5.011981630919637</v>
+      </c>
+      <c r="K59">
+        <v>0.38740920096852299</v>
+      </c>
+      <c r="L59">
+        <v>0.47494426674421741</v>
+      </c>
+      <c r="M59">
+        <v>1.7150096843552514</v>
+      </c>
+      <c r="N59">
+        <v>0.6295399515738499</v>
+      </c>
+      <c r="O59">
+        <v>0.75118736066686043</v>
+      </c>
+      <c r="P59">
+        <v>4.4403301018920853</v>
+      </c>
+      <c r="Q59">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -2208,22 +3792,49 @@
         <v>1.5543541224174464</v>
       </c>
       <c r="D60">
+        <v>-0.42758458035823554</v>
+      </c>
+      <c r="E60">
         <v>0.52986512524084772</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>0.48754585827379371</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
       <c r="G60">
+        <v>-7.755834727802406</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
         <v>-4.344468044024382E-2</v>
       </c>
-      <c r="H60">
+      <c r="J60">
+        <v>-16.778537736016315</v>
+      </c>
+      <c r="K60">
+        <v>0.91522157996146436</v>
+      </c>
+      <c r="L60">
+        <v>0.83993048851130003</v>
+      </c>
+      <c r="M60">
+        <v>3.6447947729780292</v>
+      </c>
+      <c r="N60">
+        <v>1.2042389210019269</v>
+      </c>
+      <c r="O60">
+        <v>1.4143657076655702</v>
+      </c>
+      <c r="P60">
+        <v>-1.157433107127358</v>
+      </c>
+      <c r="Q60">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -2234,50 +3845,103 @@
         <v>2.4176760030280047</v>
       </c>
       <c r="D61">
+        <v>11.855436431889704</v>
+      </c>
+      <c r="E61">
         <v>0.708215297450425</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0.64345193035578674</v>
       </c>
-      <c r="F61">
+      <c r="G61">
+        <v>10.280411549142524</v>
+      </c>
+      <c r="H61">
         <v>0.2360717658168083</v>
       </c>
-      <c r="G61">
+      <c r="I61">
         <v>0.15613171839514228</v>
       </c>
-      <c r="H61">
+      <c r="J61">
+        <v>7.6286946383498169</v>
+      </c>
+      <c r="K61">
+        <v>1.0859301227573182</v>
+      </c>
+      <c r="L61">
+        <v>1.1496971990915843</v>
+      </c>
+      <c r="M61">
+        <v>5.0135086682896119</v>
+      </c>
+      <c r="N61">
+        <v>1.5580736543909348</v>
+      </c>
+      <c r="O61">
+        <v>1.6843300529901548</v>
+      </c>
+      <c r="P61">
+        <v>5.1699146918186951</v>
+      </c>
+      <c r="Q61">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62">
         <v>1.1494252873563218</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62">
         <v>1.5821911507680819</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62">
+        <v>-12.473215539379998</v>
+      </c>
+      <c r="E62">
         <v>0.45977011494252873</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62">
         <v>0.44614110937355439</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62">
+        <v>-9.9309007362456256</v>
+      </c>
+      <c r="H62">
         <v>9.1954022988505746E-2</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62">
         <v>0.12878300064390247</v>
       </c>
-      <c r="H62">
+      <c r="J62">
+        <v>-7.8819147395342517</v>
+      </c>
+      <c r="K62">
+        <v>0.64367816091954022</v>
+      </c>
+      <c r="L62">
+        <v>0.73590286082237155</v>
+      </c>
+      <c r="M62">
+        <v>2.4359440384107884</v>
+      </c>
+      <c r="N62">
+        <v>0.82758620689655171</v>
+      </c>
+      <c r="O62">
+        <v>0.94747493330879906</v>
+      </c>
+      <c r="P62">
+        <v>0.24908082394567455</v>
+      </c>
+      <c r="Q62">
         <v>60</v>
       </c>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63">
@@ -2287,23 +3951,50 @@
         <v>0.21343873517786924</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>-4.9472136161225029</v>
       </c>
       <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>5.5335968379450234E-2</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
       <c r="G63">
-        <v>0</v>
+        <v>-11.08134555772193</v>
       </c>
       <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>-11.165724151295747</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>4.3478260869561622E-2</v>
+      </c>
+      <c r="M63">
+        <v>-0.1943301224673262</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0.14229249011857348</v>
+      </c>
+      <c r="P63">
+        <v>5.2891012424604078</v>
+      </c>
+      <c r="Q63">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64">
@@ -2313,23 +4004,50 @@
         <v>0.26397337312062785</v>
       </c>
       <c r="D64">
+        <v>3.2620493645306334</v>
+      </c>
+      <c r="E64">
         <v>3.8255547054322873E-2</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>0.1453766402693363</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
       <c r="G64">
+        <v>2.282368711340641</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>1.9128505298595968E-2</v>
       </c>
-      <c r="H64">
+      <c r="J64">
+        <v>-5.3259548538529771</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0.13772523814988749</v>
+      </c>
+      <c r="M64">
+        <v>4.7473860777860883</v>
+      </c>
+      <c r="N64">
+        <v>0.15302218821729149</v>
+      </c>
+      <c r="O64">
+        <v>0.30605608477753549</v>
+      </c>
+      <c r="P64">
+        <v>6.6283206645469246</v>
+      </c>
+      <c r="Q64">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65">
@@ -2339,23 +4057,50 @@
         <v>0.1746031746031782</v>
       </c>
       <c r="D65">
+        <v>-4.6762225595935725</v>
+      </c>
+      <c r="E65">
         <v>7.9365079365079361E-2</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>0.19047619047619771</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
       <c r="G65">
+        <v>-0.99575176327496173</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
         <v>3.9682539682503589E-3</v>
       </c>
-      <c r="H65">
+      <c r="J65">
+        <v>-7.664734596947925</v>
+      </c>
+      <c r="K65">
+        <v>7.9365079365079361E-2</v>
+      </c>
+      <c r="L65">
+        <v>0.15873015873015872</v>
+      </c>
+      <c r="M65">
+        <v>-0.8259383747779373</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0.38095238095237738</v>
+      </c>
+      <c r="P65">
+        <v>4.3320845483255654</v>
+      </c>
+      <c r="Q65">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66">
@@ -2365,23 +4110,50 @@
         <v>0.45320121365747701</v>
       </c>
       <c r="D66">
+        <v>6.6989327561573306</v>
+      </c>
+      <c r="E66">
         <v>0.19201228878648233</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>0.27652955409608704</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
       <c r="G66">
+        <v>2.5872470807484484</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
         <v>1.9203441256673198E-2</v>
       </c>
-      <c r="H66">
+      <c r="J66">
+        <v>1.4781695836236608</v>
+      </c>
+      <c r="K66">
+        <v>0.19201228878648233</v>
+      </c>
+      <c r="L66">
+        <v>0.3687060721281219</v>
+      </c>
+      <c r="M66">
+        <v>9.1148910650975257</v>
+      </c>
+      <c r="N66">
+        <v>0.26881720430107531</v>
+      </c>
+      <c r="O66">
+        <v>0.4992894726735031</v>
+      </c>
+      <c r="P66">
+        <v>5.4903895720403089</v>
+      </c>
+      <c r="Q66">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67">
@@ -2391,23 +4163,50 @@
         <v>0.78264094955489272</v>
       </c>
       <c r="D67">
+        <v>1.9296961619422897</v>
+      </c>
+      <c r="E67">
         <v>0.22255192878338279</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>0.43026706231453665</v>
       </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
       <c r="G67">
+        <v>-8.0228619529573372E-4</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
         <v>7.4183976261060127E-3</v>
       </c>
-      <c r="H67">
+      <c r="J67">
+        <v>-5.3972108700403174</v>
+      </c>
+      <c r="K67">
+        <v>0.25964391691394656</v>
+      </c>
+      <c r="L67">
+        <v>1.1127596439169141</v>
+      </c>
+      <c r="M67">
+        <v>5.9848856046491701</v>
+      </c>
+      <c r="N67">
+        <v>0.25964391691394656</v>
+      </c>
+      <c r="O67">
+        <v>0.57492581602373882</v>
+      </c>
+      <c r="P67">
+        <v>2.9504648332878158</v>
+      </c>
+      <c r="Q67">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68">
@@ -2417,23 +4216,50 @@
         <v>0.62755798090041237</v>
       </c>
       <c r="D68">
+        <v>-9.3652347548987187</v>
+      </c>
+      <c r="E68">
         <v>6.8212824010914053E-2</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>0.12278308321964218</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
       <c r="G68">
+        <v>-15.501391368968573</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
         <v>3.0695770804914424E-2</v>
       </c>
-      <c r="H68">
+      <c r="J68">
+        <v>-15.087006735218027</v>
+      </c>
+      <c r="K68">
+        <v>6.8212824010914053E-2</v>
+      </c>
+      <c r="L68">
+        <v>0.17735334242837034</v>
+      </c>
+      <c r="M68">
+        <v>-8.0233299891478644</v>
+      </c>
+      <c r="N68">
+        <v>0.20463847203274216</v>
+      </c>
+      <c r="O68">
+        <v>0.25920873124147031</v>
+      </c>
+      <c r="P68">
+        <v>3.5893790644086239</v>
+      </c>
+      <c r="Q68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69">
@@ -2443,23 +4269,50 @@
         <v>0.42185616713539575</v>
       </c>
       <c r="D69">
+        <v>14.581164423335096</v>
+      </c>
+      <c r="E69">
         <v>4.0176777822418644E-2</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>6.4282844515866175E-2</v>
       </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
       <c r="G69">
-        <v>0</v>
+        <v>-11.228488367377988</v>
       </c>
       <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>-12.227047175483222</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0.14061872237846523</v>
+      </c>
+      <c r="M69">
+        <v>10.915514381085112</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0.43390920048212867</v>
+      </c>
+      <c r="P69">
+        <v>1.0616494769798874</v>
+      </c>
+      <c r="Q69">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70">
@@ -2469,23 +4322,50 @@
         <v>0.987418985894018</v>
       </c>
       <c r="D70">
+        <v>-1.1203535633904413</v>
+      </c>
+      <c r="E70">
         <v>0.15249714067861228</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>0.2821197102554362</v>
       </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
       <c r="G70">
+        <v>9.2149795713580573</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
         <v>2.6686999618750214E-2</v>
       </c>
-      <c r="H70">
+      <c r="J70">
+        <v>-3.1465662792423648</v>
+      </c>
+      <c r="K70">
+        <v>0.30499428135722456</v>
+      </c>
+      <c r="L70">
+        <v>0.56805184902783423</v>
+      </c>
+      <c r="M70">
+        <v>-0.72367886802382986</v>
+      </c>
+      <c r="N70">
+        <v>0.30499428135722456</v>
+      </c>
+      <c r="O70">
+        <v>0.72054898970644654</v>
+      </c>
+      <c r="P70">
+        <v>7.3257370645755122</v>
+      </c>
+      <c r="Q70">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71">
@@ -2495,23 +4375,50 @@
         <v>2.3324348607367509</v>
       </c>
       <c r="D71">
+        <v>-7.4018925026340003</v>
+      </c>
+      <c r="E71">
         <v>0.64631956912028721</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>0.76549865229111158</v>
       </c>
-      <c r="F71">
+      <c r="G71">
+        <v>-11.375572687269146</v>
+      </c>
+      <c r="H71">
         <v>3.5906642728904849E-2</v>
       </c>
-      <c r="G71">
+      <c r="I71">
         <v>3.5938903863432167E-2</v>
       </c>
-      <c r="H71">
+      <c r="J71">
+        <v>-13.403036456842971</v>
+      </c>
+      <c r="K71">
+        <v>1.0053859964093357</v>
+      </c>
+      <c r="L71">
+        <v>1.099730458221021</v>
+      </c>
+      <c r="M71">
+        <v>-4.0962151829335784</v>
+      </c>
+      <c r="N71">
+        <v>1.1490125673249552</v>
+      </c>
+      <c r="O71">
+        <v>1.2973944294698978</v>
+      </c>
+      <c r="P71">
+        <v>-4.2862919565873288</v>
+      </c>
+      <c r="Q71">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72">
@@ -2521,23 +4428,50 @@
         <v>1.255611435514896</v>
       </c>
       <c r="D72">
+        <v>16.871728008038396</v>
+      </c>
+      <c r="E72">
         <v>0.50607287449392713</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>0.56705032571639813</v>
       </c>
-      <c r="F72">
+      <c r="G72">
+        <v>2.5758445146983728</v>
+      </c>
+      <c r="H72">
         <v>3.3738191632928474E-2</v>
       </c>
-      <c r="G72">
+      <c r="I72">
         <v>3.0377696020509545E-2</v>
       </c>
-      <c r="H72">
+      <c r="J72">
+        <v>-17.808180356654095</v>
+      </c>
+      <c r="K72">
+        <v>0.40485829959514169</v>
+      </c>
+      <c r="L72">
+        <v>1.4783812063320527</v>
+      </c>
+      <c r="M72">
+        <v>7.4126769301291997</v>
+      </c>
+      <c r="N72">
+        <v>0.40485829959514169</v>
+      </c>
+      <c r="O72">
+        <v>3.8377155972592512</v>
+      </c>
+      <c r="P72">
+        <v>7.6024122586114542</v>
+      </c>
+      <c r="Q72">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73">
@@ -2547,23 +4481,50 @@
         <v>0.26223776223776224</v>
       </c>
       <c r="D73">
+        <v>-5.0385209852770076</v>
+      </c>
+      <c r="E73">
         <v>0.1048951048951049</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0.14335664335664017</v>
       </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
       <c r="G73">
-        <v>0</v>
+        <v>-11.683221794541515</v>
       </c>
       <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>-10.106453463486302</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0.14335664335664017</v>
+      </c>
+      <c r="M73">
+        <v>-1.660985797367913</v>
+      </c>
+      <c r="N73">
+        <v>0.17482517482517482</v>
+      </c>
+      <c r="O73">
+        <v>0.37412587412586779</v>
+      </c>
+      <c r="P73">
+        <v>-7.0530972019968452</v>
+      </c>
+      <c r="Q73">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74">
@@ -2573,23 +4534,50 @@
         <v>0.19898819561551739</v>
       </c>
       <c r="D74">
+        <v>9.0965710111239204</v>
+      </c>
+      <c r="E74">
         <v>0.1011804384485666</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>0.13490725126475547</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
       <c r="G74">
+        <v>2.4072212986301005</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
         <v>3.3726812816158194E-3</v>
       </c>
-      <c r="H74">
+      <c r="J74">
+        <v>-0.27170728046846004</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>9.1062394603703814E-2</v>
+      </c>
+      <c r="M74">
+        <v>6.3289683314597029</v>
+      </c>
+      <c r="N74">
+        <v>6.7453625632377737E-2</v>
+      </c>
+      <c r="O74">
+        <v>0.19224283305227041</v>
+      </c>
+      <c r="P74">
+        <v>0.81604539223230599</v>
+      </c>
+      <c r="Q74">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75">
@@ -2599,23 +4587,50 @@
         <v>0.13636363636363955</v>
       </c>
       <c r="D75">
+        <v>-11.874481751257312</v>
+      </c>
+      <c r="E75">
         <v>3.4965034965034968E-2</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>8.0419580419586786E-2</v>
       </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
       <c r="G75">
-        <v>0</v>
+        <v>14.017163674285458</v>
       </c>
       <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>10.426087439626849</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>2.4475524475518116E-2</v>
+      </c>
+      <c r="M75">
+        <v>-8.6290772953748434</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0.17482517482517482</v>
+      </c>
+      <c r="P75">
+        <v>5.0337634185370552</v>
+      </c>
+      <c r="Q75">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76">
@@ -2625,23 +4640,50 @@
         <v>0.34190927555856154</v>
       </c>
       <c r="D76">
+        <v>-8.7332653676677161</v>
+      </c>
+      <c r="E76">
         <v>0.13540961408259986</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>0.2200406228842248</v>
       </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
       <c r="G76">
-        <v>0</v>
+        <v>3.2791653549091944</v>
       </c>
       <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.4539558781659858</v>
+      </c>
+      <c r="K76">
+        <v>6.7704807041299928E-2</v>
+      </c>
+      <c r="L76">
+        <v>0.34190927555856154</v>
+      </c>
+      <c r="M76">
+        <v>-3.9805155200033449</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0.21665538253216288</v>
+      </c>
+      <c r="P76">
+        <v>-2.4550355747256765</v>
+      </c>
+      <c r="Q76">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77">
@@ -2651,23 +4693,50 @@
         <v>0.87807733584832015</v>
       </c>
       <c r="D77">
+        <v>1.1173688793625476</v>
+      </c>
+      <c r="E77">
         <v>0.42276422764227645</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>0.59514130540831178</v>
       </c>
-      <c r="F77">
+      <c r="G77">
+        <v>3.1051987891230466</v>
+      </c>
+      <c r="H77">
         <v>3.2520325203252029E-2</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>3.9025659371045324E-2</v>
       </c>
-      <c r="H77">
+      <c r="J77">
+        <v>5.8171209550089777</v>
+      </c>
+      <c r="K77">
+        <v>0.42276422764227645</v>
+      </c>
+      <c r="L77">
+        <v>1.8016846076295192</v>
+      </c>
+      <c r="M77">
+        <v>1.7042788283713066</v>
+      </c>
+      <c r="N77">
+        <v>0.42276422764227645</v>
+      </c>
+      <c r="O77">
+        <v>1.0211714202087903</v>
+      </c>
+      <c r="P77">
+        <v>6.710349318751355</v>
+      </c>
+      <c r="Q77">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78">
@@ -2677,23 +4746,50 @@
         <v>0.87980912615568152</v>
       </c>
       <c r="D78">
+        <v>19.730569824107665</v>
+      </c>
+      <c r="E78">
         <v>0.23859230539815093</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>0.31315240083507306</v>
       </c>
-      <c r="F78">
+      <c r="G78">
+        <v>-11.469114186498034</v>
+      </c>
+      <c r="H78">
         <v>2.9824038174768867E-2</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>4.1753653444679122E-2</v>
       </c>
-      <c r="H78">
+      <c r="J78">
+        <v>-6.7290690821905921</v>
+      </c>
+      <c r="K78">
+        <v>0.14912019087384432</v>
+      </c>
+      <c r="L78">
+        <v>0.53086787951089121</v>
+      </c>
+      <c r="M78">
+        <v>3.4276744139581434</v>
+      </c>
+      <c r="N78">
+        <v>0.23859230539815093</v>
+      </c>
+      <c r="O78">
+        <v>0.81717864598866952</v>
+      </c>
+      <c r="P78">
+        <v>1.7295409302712437</v>
+      </c>
+      <c r="Q78">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79">
@@ -2703,23 +4799,50 @@
         <v>0.42290060058993179</v>
       </c>
       <c r="D79">
+        <v>18.937256779477728</v>
+      </c>
+      <c r="E79">
         <v>0.24875621890547264</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>0.26298020540886635</v>
       </c>
-      <c r="F79">
+      <c r="G79">
+        <v>15.84495310374133</v>
+      </c>
+      <c r="H79">
         <v>3.5536602700781808E-2</v>
       </c>
-      <c r="G79">
+      <c r="I79">
         <v>4.2645438714960474E-2</v>
       </c>
-      <c r="H79">
+      <c r="J79">
+        <v>-5.1223730270568932</v>
+      </c>
+      <c r="K79">
+        <v>0.28429282160625446</v>
+      </c>
+      <c r="L79">
+        <v>0.30562564412381066</v>
+      </c>
+      <c r="M79">
+        <v>1.8714221821079495</v>
+      </c>
+      <c r="N79">
+        <v>0.28429282160625446</v>
+      </c>
+      <c r="O79">
+        <v>0.34116350971960302</v>
+      </c>
+      <c r="P79">
+        <v>3.7193971442006153</v>
+      </c>
+      <c r="Q79">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80">
@@ -2729,23 +4852,50 @@
         <v>0.78035654221324646</v>
       </c>
       <c r="D80">
+        <v>-13.101694632802513</v>
+      </c>
+      <c r="E80">
         <v>0.20181634712411706</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>0.33299697275479617</v>
       </c>
-      <c r="F80">
+      <c r="G80">
+        <v>10.795939695896065</v>
+      </c>
+      <c r="H80">
         <v>3.3636057854019512E-2</v>
       </c>
-      <c r="G80">
+      <c r="I80">
         <v>4.7090480995630374E-2</v>
       </c>
-      <c r="H80">
+      <c r="J80">
+        <v>2.9323192141332739</v>
+      </c>
+      <c r="K80">
+        <v>0.26908846283215609</v>
+      </c>
+      <c r="L80">
+        <v>0.68953918600739994</v>
+      </c>
+      <c r="M80">
+        <v>-2.5126860121468066</v>
+      </c>
+      <c r="N80">
+        <v>0.26908846283215609</v>
+      </c>
+      <c r="O80">
+        <v>0.7702657248570498</v>
+      </c>
+      <c r="P80">
+        <v>7.4499279000778049</v>
+      </c>
+      <c r="Q80">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81">
@@ -2755,23 +4905,50 @@
         <v>2.4368658933594585</v>
       </c>
       <c r="D81">
+        <v>13.707907775040976</v>
+      </c>
+      <c r="E81">
         <v>0.44233807266982628</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>0.63213123044344</v>
       </c>
-      <c r="F81">
+      <c r="G81">
+        <v>-11.31397277981919</v>
+      </c>
+      <c r="H81">
         <v>6.3191153238546599E-2</v>
       </c>
-      <c r="G81">
+      <c r="I81">
         <v>0.11694427763204504</v>
       </c>
-      <c r="H81">
+      <c r="J81">
+        <v>-5.8569423328789041</v>
+      </c>
+      <c r="K81">
+        <v>0.63191153238546605</v>
+      </c>
+      <c r="L81">
+        <v>1.6625051360662442</v>
+      </c>
+      <c r="M81">
+        <v>4.1810530875369754</v>
+      </c>
+      <c r="N81">
+        <v>1.3586097946287519</v>
+      </c>
+      <c r="O81">
+        <v>1.7668067890894177</v>
+      </c>
+      <c r="P81">
+        <v>-9.8299691033109688</v>
+      </c>
+      <c r="Q81">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82">
@@ -2781,23 +4958,50 @@
         <v>1.0220056121695438</v>
       </c>
       <c r="D82">
+        <v>3.8728638762844616</v>
+      </c>
+      <c r="E82">
         <v>0.59066745422327227</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>0.70595185349283973</v>
       </c>
-      <c r="F82">
+      <c r="G82">
+        <v>5.3014303856096383</v>
+      </c>
+      <c r="H82">
         <v>5.9066745422327233E-2</v>
       </c>
-      <c r="G82">
+      <c r="I82">
         <v>0.10633584404075938</v>
       </c>
-      <c r="H82">
+      <c r="J82">
+        <v>-9.9295202749250002</v>
+      </c>
+      <c r="K82">
+        <v>0.59066745422327227</v>
+      </c>
+      <c r="L82">
+        <v>3.0719243833997933</v>
+      </c>
+      <c r="M82">
+        <v>2.4933666732397626</v>
+      </c>
+      <c r="N82">
+        <v>0.67926757235676316</v>
+      </c>
+      <c r="O82">
+        <v>0.87136316644513367</v>
+      </c>
+      <c r="P82">
+        <v>-9.0945196772269998</v>
+      </c>
+      <c r="Q82">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83">
@@ -2807,23 +5011,50 @@
         <v>0.20576131687242799</v>
       </c>
       <c r="D83">
+        <v>8.829135398431772</v>
+      </c>
+      <c r="E83">
         <v>0.12662234884457108</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>0.22158911047799934</v>
       </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
       <c r="G83">
+        <v>1.0428767680157844</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
         <v>2.5324469768919972E-2</v>
       </c>
-      <c r="H83">
+      <c r="J83">
+        <v>-1.9432507302082884</v>
+      </c>
+      <c r="K83">
+        <v>9.4966761633428307E-2</v>
+      </c>
+      <c r="L83">
+        <v>0.12662234884457108</v>
+      </c>
+      <c r="M83">
+        <v>7.5195383920348791</v>
+      </c>
+      <c r="N83">
+        <v>9.4966761633428307E-2</v>
+      </c>
+      <c r="O83">
+        <v>1.2250712250712192</v>
+      </c>
+      <c r="P83">
+        <v>3.8289392329838101</v>
+      </c>
+      <c r="Q83">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84">
@@ -2833,23 +5064,50 @@
         <v>0.19143117593437198</v>
       </c>
       <c r="D84">
+        <v>20.233475788733767</v>
+      </c>
+      <c r="E84">
         <v>9.1157702825888781E-2</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>0.19446976602856553</v>
       </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
       <c r="G84">
-        <v>0</v>
+        <v>-14.392871569711637</v>
       </c>
       <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>-6.7089332397066617</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>9.1157702825888781E-2</v>
+      </c>
+      <c r="M84">
+        <v>8.099629698208485</v>
+      </c>
+      <c r="N84">
+        <v>9.1157702825888781E-2</v>
+      </c>
+      <c r="O84">
+        <v>0.68368277119416598</v>
+      </c>
+      <c r="P84">
+        <v>9.3726249052162682</v>
+      </c>
+      <c r="Q84">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85">
@@ -2859,23 +5117,50 @@
         <v>0.14733542319748646</v>
       </c>
       <c r="D85">
+        <v>-7.8273926122321438</v>
+      </c>
+      <c r="E85">
         <v>0.12539184952978058</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>0.17241379310344829</v>
       </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
       <c r="G85">
+        <v>-10.131675195698858</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
         <v>3.1347962382445145E-2</v>
       </c>
-      <c r="H85">
+      <c r="J85">
+        <v>1.8457956145353265</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0.11598746081504133</v>
+      </c>
+      <c r="M85">
+        <v>-9.0051458163497653</v>
+      </c>
+      <c r="N85">
+        <v>3.1347962382445145E-2</v>
+      </c>
+      <c r="O85">
+        <v>0.2946708463949872</v>
+      </c>
+      <c r="P85">
+        <v>4.3930427739551341</v>
+      </c>
+      <c r="Q85">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86">
@@ -2885,23 +5170,50 @@
         <v>0.2553967771359103</v>
       </c>
       <c r="D86">
+        <v>10.37911989844471</v>
+      </c>
+      <c r="E86">
         <v>6.0808756460930376E-2</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>0.23715415019763397</v>
       </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
       <c r="G86">
-        <v>0</v>
+        <v>2.2496862669298578</v>
       </c>
       <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>8.1715450035200039</v>
+      </c>
+      <c r="K86">
+        <v>9.1213134691395567E-2</v>
+      </c>
+      <c r="L86">
+        <v>0.28580115536637551</v>
+      </c>
+      <c r="M86">
+        <v>4.029374726312005</v>
+      </c>
+      <c r="N86">
+        <v>9.1213134691395567E-2</v>
+      </c>
+      <c r="O86">
+        <v>1.2161751292186074</v>
+      </c>
+      <c r="P86">
+        <v>2.8340586513095847</v>
+      </c>
+      <c r="Q86">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87">
@@ -2911,23 +5223,50 @@
         <v>0.76011299764102602</v>
       </c>
       <c r="D87">
+        <v>1.5242924615254294</v>
+      </c>
+      <c r="E87">
         <v>0.34944670937682004</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>0.5300404811136622</v>
       </c>
-      <c r="F87">
+      <c r="G87">
+        <v>-4.9328239610358091</v>
+      </c>
+      <c r="H87">
         <v>5.8241118229470007E-2</v>
       </c>
-      <c r="G87">
+      <c r="I87">
         <v>8.7369310073681455E-2</v>
       </c>
-      <c r="H87">
+      <c r="J87">
+        <v>-0.4509441734311766</v>
+      </c>
+      <c r="K87">
+        <v>0.64065230052416999</v>
+      </c>
+      <c r="L87">
+        <v>2.0706526487462478</v>
+      </c>
+      <c r="M87">
+        <v>0.2093734438321446</v>
+      </c>
+      <c r="N87">
+        <v>0.46592894583576006</v>
+      </c>
+      <c r="O87">
+        <v>0.74846375629786577</v>
+      </c>
+      <c r="P87">
+        <v>4.3854279549615649</v>
+      </c>
+      <c r="Q87">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88">
@@ -2937,23 +5276,50 @@
         <v>0.70168885568687411</v>
       </c>
       <c r="D88">
+        <v>2.2490533052651038</v>
+      </c>
+      <c r="E88">
         <v>0.37333333333333335</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>0.43221899095541255</v>
       </c>
-      <c r="F88">
+      <c r="G88">
+        <v>-13.603843540364281</v>
+      </c>
+      <c r="H88">
         <v>5.3333333333333337E-2</v>
       </c>
-      <c r="G88">
+      <c r="I88">
         <v>4.8024332328372429E-2</v>
       </c>
-      <c r="H88">
+      <c r="J88">
+        <v>-12.440239774411459</v>
+      </c>
+      <c r="K88">
+        <v>0.37333333333333335</v>
+      </c>
+      <c r="L88">
+        <v>0.94181051732877274</v>
+      </c>
+      <c r="M88">
+        <v>5.4556992209681274</v>
+      </c>
+      <c r="N88">
+        <v>0.37333333333333335</v>
+      </c>
+      <c r="O88">
+        <v>0.5816280248659248</v>
+      </c>
+      <c r="P88">
+        <v>2.3820079744336202</v>
+      </c>
+      <c r="Q88">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89">
@@ -2963,23 +5329,50 @@
         <v>0.37524053880692171</v>
       </c>
       <c r="D89">
+        <v>5.8569408699292627</v>
+      </c>
+      <c r="E89">
         <v>0.25657472738935211</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>0.32392559332905413</v>
       </c>
-      <c r="F89">
+      <c r="G89">
+        <v>-16.118680333244431</v>
+      </c>
+      <c r="H89">
         <v>3.2071840923669014E-2</v>
       </c>
-      <c r="G89">
+      <c r="I89">
         <v>3.2071840923669014E-2</v>
       </c>
-      <c r="H89">
+      <c r="J89">
+        <v>-6.8609082077931429</v>
+      </c>
+      <c r="K89">
+        <v>0.25657472738935211</v>
+      </c>
+      <c r="L89">
+        <v>0.32713277742141816</v>
+      </c>
+      <c r="M89">
+        <v>11.077827426002147</v>
+      </c>
+      <c r="N89">
+        <v>0.25657472738935211</v>
+      </c>
+      <c r="O89">
+        <v>0.90763309813983906</v>
+      </c>
+      <c r="P89">
+        <v>15.023999032174402</v>
+      </c>
+      <c r="Q89">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90">
@@ -2989,23 +5382,50 @@
         <v>0.67189249720044242</v>
       </c>
       <c r="D90">
+        <v>-0.38934065935615031</v>
+      </c>
+      <c r="E90">
         <v>0.30257186081694404</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>0.36621167640204322</v>
       </c>
-      <c r="F90">
+      <c r="G90">
+        <v>0.37691145551371824</v>
+      </c>
+      <c r="H90">
         <v>9.0771558245083206E-2</v>
       </c>
-      <c r="G90">
+      <c r="I90">
         <v>8.1716655064913837E-2</v>
       </c>
-      <c r="H90">
+      <c r="J90">
+        <v>-2.3383565820637093</v>
+      </c>
+      <c r="K90">
+        <v>0.36308623298033282</v>
+      </c>
+      <c r="L90">
+        <v>0.41766290366513509</v>
+      </c>
+      <c r="M90">
+        <v>3.274551717097371</v>
+      </c>
+      <c r="N90">
+        <v>0.36308623298033282</v>
+      </c>
+      <c r="O90">
+        <v>0.6961048394419056</v>
+      </c>
+      <c r="P90">
+        <v>-0.87283702344416025</v>
+      </c>
+      <c r="Q90">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91">
@@ -3015,23 +5435,50 @@
         <v>2.3144475920679835</v>
       </c>
       <c r="D91">
+        <v>19.014553637915199</v>
+      </c>
+      <c r="E91">
         <v>0.48131370328425821</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>0.79603399433427502</v>
       </c>
-      <c r="F91">
+      <c r="G91">
+        <v>-13.412381970229676</v>
+      </c>
+      <c r="H91">
         <v>0.11325028312570783</v>
       </c>
-      <c r="G91">
+      <c r="I91">
         <v>0.14164305949008499</v>
       </c>
-      <c r="H91">
+      <c r="J91">
+        <v>-6.048818949003814</v>
+      </c>
+      <c r="K91">
+        <v>0.70781426953567383</v>
+      </c>
+      <c r="L91">
+        <v>0.96033994334277872</v>
+      </c>
+      <c r="M91">
+        <v>9.1076922896951942</v>
+      </c>
+      <c r="N91">
+        <v>0.76443941109852775</v>
+      </c>
+      <c r="O91">
+        <v>1.1246458923512697</v>
+      </c>
+      <c r="P91">
+        <v>3.7306807961580035</v>
+      </c>
+      <c r="Q91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92">
@@ -3041,29 +5488,56 @@
         <v>0.91418304798140881</v>
       </c>
       <c r="D92">
+        <v>11.888626085171195</v>
+      </c>
+      <c r="E92">
         <v>0.52826201796090866</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>0.63939970407948299</v>
       </c>
-      <c r="F92">
+      <c r="G92">
+        <v>-2.2995891953094572</v>
+      </c>
+      <c r="H92">
         <v>0.10565240359218173</v>
       </c>
-      <c r="G92">
+      <c r="I92">
         <v>0.10040160642570761</v>
       </c>
-      <c r="H92">
+      <c r="J92">
+        <v>-5.3733774126361631</v>
+      </c>
+      <c r="K92">
+        <v>0.73956682514527206</v>
+      </c>
+      <c r="L92">
+        <v>3.1018812090467156</v>
+      </c>
+      <c r="M92">
+        <v>1.0640398358503462</v>
+      </c>
+      <c r="N92">
+        <v>0.52826201796090866</v>
+      </c>
+      <c r="O92">
+        <v>0.79000211371803242</v>
+      </c>
+      <c r="P92">
+        <v>3.0297453362642024</v>
+      </c>
+      <c r="Q92">
         <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiment1.xlsx
+++ b/experiment1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\CTOP\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E264F5F0-07E1-4B7A-9B14-92424F48D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B20A1C-6465-4161-9BC0-E278AAE784D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-6810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="set2" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -388,10 +388,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,36 +681,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="I1" s="2"/>
+      <c r="K1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3"/>
       <c r="B2" t="s">
         <v>3</v>
       </c>
